--- a/artfynd/A 38686-2021 artfynd.xlsx
+++ b/artfynd/A 38686-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38686-2021 artfynd.xlsx
+++ b/artfynd/A 38686-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89087437</v>
       </c>
       <c r="B2" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750788.3443989656</v>
+        <v>750788</v>
       </c>
       <c r="R2" t="n">
-        <v>7089862.722689836</v>
+        <v>7089863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2020-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,55 +776,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71570509</v>
+        <v>117772088</v>
       </c>
       <c r="B3" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>101978</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Springkornsfältmätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Xanthorhoe biriviata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Borkhausen, 1794)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baggböle, Vb</t>
+          <t>Kåddis, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750850.3687650872</v>
+        <v>750894</v>
       </c>
       <c r="R3" t="n">
-        <v>7089808.334774029</v>
+        <v>7089823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,33 +872,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>71570532</v>
+        <v>120507051</v>
       </c>
       <c r="B4" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,42 +902,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>102185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arboretrum norr, Vb</t>
+          <t>Strandpromenaden, Kåddis, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750850.3687650872</v>
+        <v>750731</v>
       </c>
       <c r="R4" t="n">
-        <v>7089808.334774029</v>
+        <v>7089867</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,16 +977,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1028,12 +1001,7 @@
         <v>71570642</v>
       </c>
       <c r="B5" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750850.3687650872</v>
+        <v>750850</v>
       </c>
       <c r="R5" t="n">
-        <v>7089808.334774029</v>
+        <v>7089808</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1069,9 @@
           <t>2018-05-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-05-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1095,210 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>71570509</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>750850</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7089808</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-05-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-05-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>71570532</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arboretrum norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>750850</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7089808</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-05-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-05-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
